--- a/checklist_forms/031_voc_waste_gas_maintenance_checklist--checklist_forms.xlsx
+++ b/checklist_forms/031_voc_waste_gas_maintenance_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>facility_info</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Main_Page</t>
+          <t>Facility Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>general_info</t>
+          <t>facility_equipment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>facility_info</t>
+          <t>Equipment Status</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>maintenance_schedule</t>
+          <t>equipment_status</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>maintenance_schedule</t>
+          <t>Equipment Status (2)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,30 +584,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>equipment_status</t>
+          <t>maintenance_schedule</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>equipment_status</t>
+          <t>Maintenance Schedule</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,53 +617,53 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>inspection_frequency</t>
+          <t>Inspection Frequency</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>comments_section</t>
+          <t>next_inspection_due</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Next Inspection Due</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>next_inspection_due</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>next_inspection_due</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>signature</t>
+          <t>technician_signature</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>signature</t>
+          <t>Technician Signature</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>technician_signature</t>
+          <t>technician_email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>technician_signature</t>
+          <t>Technician Email</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,58 +727,58 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>facility_id</t>
+          <t>manager_signature</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>facility_id</t>
+          <t>Manager Signature</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>manager_email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>Manager Email</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>last_inspection_date</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>Last Inspection Date</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>last_inspection_time</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>Last Inspection Time</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>last_updated_by</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>updated_by</t>
+          <t>Last Updated By</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>last_updated_time</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>Last Updated Time</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>deleted_by</t>
+          <t>last_deleted_by</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>deleted_by</t>
+          <t>Last Deleted By</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,338 +888,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>last_deleted_time</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>deleted_at</t>
+          <t>Last Deleted Time</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>deleted_by</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>deleted_by</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>deleted_at</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>deleted_at</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>deleted_at</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>deleted_at</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>deleted_by</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>deleted_by</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>deleted_at</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>deleted_at</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>deleted_at</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>deleted_at</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>deleted_by</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>deleted_by</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>deleted_at</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>deleted_at</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>facility_name</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>facility_name</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>facility_address</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>facility_address</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>facility_city</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>facility_city</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>facility_state</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>facility_state</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>facility_country</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>facility_country</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>facility_zip</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>facility_zip</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1236,12 +914,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1264,34 +942,238 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>maintenance_schedule_choices</t>
+          <t>facility_equipment_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>working</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Working</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>facility_equipment_choices</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>not_working</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Not Working</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>equipment_status_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>equipment_status_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>maintenance_schedule_choices</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>maintenance_schedule_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>maintenance_schedule_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>maintenance_schedule_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>maintenance_schedule_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Yearly</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>inspection_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>inspection_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>inspection_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>inspection_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>inspection_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
